--- a/sampleprojects/TaxReturn/excel/states/AZ.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/AZ.xlsx
@@ -84,7 +84,7 @@
     <t>MFJ/QSS: taxable_income = max(AGI - 31,500, 0); tax = taxable_income * 2.5%</t>
   </si>
   <si>
-    <t>set result.az_taxable_income = the maximum of (result.agi - 31500.0) and 0.0; set result.az_state_tax = result.az_taxable_income * 0.025</t>
+    <t>set result.az_taxable_income = the maximum of (result.state_calc_agi - 31500.0) and 0.0; set result.az_state_tax = result.az_taxable_income * 0.025</t>
   </si>
   <si>
     <t>X</t>
@@ -93,7 +93,7 @@
     <t>HOH: taxable_income = max(AGI - 15,750, 0); tax = taxable_income * 2.5%</t>
   </si>
   <si>
-    <t>set result.az_taxable_income = the maximum of (result.agi - 15750.0) and 0.0; set result.az_state_tax = result.az_taxable_income * 0.025</t>
+    <t>set result.az_taxable_income = the maximum of (result.state_calc_agi - 15750.0) and 0.0; set result.az_state_tax = result.az_taxable_income * 0.025</t>
   </si>
   <si>
     <t>Default (Single/MFS): taxable_income = max(AGI - 15,750, 0); tax = taxable_income * 2.5%</t>
